--- a/logs/fiber-change.xlsx
+++ b/logs/fiber-change.xlsx
@@ -5,21 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Uni\RWTHCES\ACOM\Neuron-C-fiber\logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dlc\Documents\Uni\CES\ACOM\Neuron-C-fiber\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E7972C-489E-4FEA-9885-2EB0898B53DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55CB089-8F39-40A1-B35D-F8E6E0045313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cmi" sheetId="2" r:id="rId1"/>
     <sheet name="Cm" sheetId="1" r:id="rId2"/>
     <sheet name="Difference" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -213,183 +210,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Cmi"/>
-      <sheetName val="Cm"/>
-      <sheetName val=""/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="B2">
-            <v>0</v>
-          </cell>
-          <cell r="C2">
-            <v>-2</v>
-          </cell>
-          <cell r="D2">
-            <v>-2</v>
-          </cell>
-          <cell r="E2">
-            <v>-2</v>
-          </cell>
-          <cell r="F2">
-            <v>-2</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>1</v>
-          </cell>
-          <cell r="C3">
-            <v>1</v>
-          </cell>
-          <cell r="D3">
-            <v>-1</v>
-          </cell>
-          <cell r="E3">
-            <v>-1</v>
-          </cell>
-          <cell r="F3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>1</v>
-          </cell>
-          <cell r="C4">
-            <v>2</v>
-          </cell>
-          <cell r="D4">
-            <v>1</v>
-          </cell>
-          <cell r="E4">
-            <v>1</v>
-          </cell>
-          <cell r="F4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>0</v>
-          </cell>
-          <cell r="C5">
-            <v>0</v>
-          </cell>
-          <cell r="D5">
-            <v>0</v>
-          </cell>
-          <cell r="E5">
-            <v>0</v>
-          </cell>
-          <cell r="F5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>-1</v>
-          </cell>
-          <cell r="C6">
-            <v>-3</v>
-          </cell>
-          <cell r="D6">
-            <v>-2</v>
-          </cell>
-          <cell r="E6">
-            <v>-3</v>
-          </cell>
-          <cell r="F6">
-            <v>-2</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>0</v>
-          </cell>
-          <cell r="C7">
-            <v>1</v>
-          </cell>
-          <cell r="D7">
-            <v>1</v>
-          </cell>
-          <cell r="E7">
-            <v>1</v>
-          </cell>
-          <cell r="F7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>-1</v>
-          </cell>
-          <cell r="C8">
-            <v>0</v>
-          </cell>
-          <cell r="D8">
-            <v>-2</v>
-          </cell>
-          <cell r="E8">
-            <v>-2</v>
-          </cell>
-          <cell r="F8">
-            <v>-1</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>-1</v>
-          </cell>
-          <cell r="C9">
-            <v>2</v>
-          </cell>
-          <cell r="D9">
-            <v>2</v>
-          </cell>
-          <cell r="E9">
-            <v>2</v>
-          </cell>
-          <cell r="F9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>0</v>
-          </cell>
-          <cell r="C10">
-            <v>2</v>
-          </cell>
-          <cell r="D10">
-            <v>3</v>
-          </cell>
-          <cell r="E10">
-            <v>3</v>
-          </cell>
-          <cell r="F10">
-            <v>2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,16 +476,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16ACA366-93DF-4268-9158-DBC0F406C09C}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.36328125" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="4" max="4" width="22.08984375" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" customWidth="1"/>
-    <col min="6" max="6" width="18.90625" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -682,7 +502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -702,7 +522,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -722,7 +542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -742,7 +562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -762,7 +582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -782,7 +602,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -802,7 +622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -822,7 +642,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -842,7 +662,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -862,12 +682,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>-3</v>
       </c>
@@ -878,7 +698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>-2</v>
       </c>
@@ -889,7 +709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>-1</v>
       </c>
@@ -900,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0</v>
       </c>
@@ -911,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
@@ -922,7 +742,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2</v>
       </c>
@@ -933,7 +753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>3</v>
       </c>
@@ -945,8 +765,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:F10">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="A15:A21">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -957,8 +777,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15:A21">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="B2:F10">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -976,16 +796,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.36328125" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" customWidth="1"/>
-    <col min="4" max="4" width="22.08984375" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" customWidth="1"/>
-    <col min="6" max="6" width="18.90625" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1002,7 +822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1022,7 +842,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1042,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1062,7 +882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1082,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1102,7 +922,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1122,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1142,7 +962,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1162,7 +982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1182,12 +1002,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>-3</v>
       </c>
@@ -1198,7 +1018,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>-2</v>
       </c>
@@ -1209,7 +1029,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>-1</v>
       </c>
@@ -1220,7 +1040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>0</v>
       </c>
@@ -1231,7 +1051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
@@ -1242,7 +1062,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2</v>
       </c>
@@ -1253,7 +1073,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>3</v>
       </c>
@@ -1265,8 +1085,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:F10">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="A15:A21">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1277,8 +1097,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15:A21">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="B2:F10">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1296,16 +1116,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6B7DC6-744F-40AD-A205-8DA839EE503C}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.08984375" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" customWidth="1"/>
-    <col min="6" max="6" width="20.453125" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1325,237 +1145,237 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <f>Cmi!B2-[1]Cm!B2</f>
+        <f>Cmi!B2-Cm!B2</f>
         <v>0</v>
       </c>
       <c r="C2">
-        <f>Cmi!C2-[1]Cm!C2</f>
+        <f>Cmi!C2-Cm!C2</f>
         <v>-1</v>
       </c>
       <c r="D2">
-        <f>Cmi!D2-[1]Cm!D2</f>
+        <f>Cmi!D2-Cm!D2</f>
         <v>0</v>
       </c>
       <c r="E2">
-        <f>Cmi!E2-[1]Cm!E2</f>
+        <f>Cmi!E2-Cm!E2</f>
         <v>-1</v>
       </c>
       <c r="F2">
-        <f>Cmi!F2-[1]Cm!F2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F2-Cm!F2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <f>Cmi!B3-[1]Cm!B3</f>
+        <f>Cmi!B3-Cm!B3</f>
         <v>0</v>
       </c>
       <c r="C3">
-        <f>Cmi!C3-[1]Cm!C3</f>
+        <f>Cmi!C3-Cm!C3</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f>Cmi!D3-[1]Cm!D3</f>
+        <f>Cmi!D3-Cm!D3</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f>Cmi!E3-[1]Cm!E3</f>
+        <f>Cmi!E3-Cm!E3</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f>Cmi!F3-[1]Cm!F3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F3-Cm!F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <f>Cmi!B4-[1]Cm!B4</f>
+        <f>Cmi!B4-Cm!B4</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f>Cmi!C4-[1]Cm!C4</f>
+        <f>Cmi!C4-Cm!C4</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f>Cmi!D4-[1]Cm!D4</f>
+        <f>Cmi!D4-Cm!D4</f>
         <v>-1</v>
       </c>
       <c r="E4">
-        <f>Cmi!E4-[1]Cm!E4</f>
+        <f>Cmi!E4-Cm!E4</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>Cmi!F4-[1]Cm!F4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F4-Cm!F4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <f>Cmi!B5-[1]Cm!B5</f>
+        <f>Cmi!B5-Cm!B5</f>
         <v>0</v>
       </c>
       <c r="C5">
-        <f>Cmi!C5-[1]Cm!C5</f>
+        <f>Cmi!C5-Cm!C5</f>
         <v>1</v>
       </c>
       <c r="D5">
-        <f>Cmi!D5-[1]Cm!D5</f>
+        <f>Cmi!D5-Cm!D5</f>
         <v>1</v>
       </c>
       <c r="E5">
-        <f>Cmi!E5-[1]Cm!E5</f>
+        <f>Cmi!E5-Cm!E5</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>Cmi!F5-[1]Cm!F5</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F5-Cm!F5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <f>Cmi!B6-[1]Cm!B6</f>
+        <f>Cmi!B6-Cm!B6</f>
         <v>1</v>
       </c>
       <c r="C6">
-        <f>Cmi!C6-[1]Cm!C6</f>
+        <f>Cmi!C6-Cm!C6</f>
         <v>1</v>
       </c>
       <c r="D6">
-        <f>Cmi!D6-[1]Cm!D6</f>
+        <f>Cmi!D6-Cm!D6</f>
         <v>1</v>
       </c>
       <c r="E6">
-        <f>Cmi!E6-[1]Cm!E6</f>
+        <f>Cmi!E6-Cm!E6</f>
         <v>2</v>
       </c>
       <c r="F6">
-        <f>Cmi!F6-[1]Cm!F6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F6-Cm!F6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7">
-        <f>Cmi!B7-[1]Cm!B7</f>
+        <f>Cmi!B7-Cm!B7</f>
         <v>0</v>
       </c>
       <c r="C7">
-        <f>Cmi!C7-[1]Cm!C7</f>
+        <f>Cmi!C7-Cm!C7</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>Cmi!D7-[1]Cm!D7</f>
+        <f>Cmi!D7-Cm!D7</f>
         <v>-1</v>
       </c>
       <c r="E7">
-        <f>Cmi!E7-[1]Cm!E7</f>
+        <f>Cmi!E7-Cm!E7</f>
         <v>-1</v>
       </c>
       <c r="F7">
-        <f>Cmi!F7-[1]Cm!F7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F7-Cm!F7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <f>Cmi!B8-[1]Cm!B8</f>
+        <f>Cmi!B8-Cm!B8</f>
         <v>0</v>
       </c>
       <c r="C8">
-        <f>Cmi!C8-[1]Cm!C8</f>
+        <f>Cmi!C8-Cm!C8</f>
         <v>-1</v>
       </c>
       <c r="D8">
-        <f>Cmi!D8-[1]Cm!D8</f>
+        <f>Cmi!D8-Cm!D8</f>
         <v>3</v>
       </c>
       <c r="E8">
-        <f>Cmi!E8-[1]Cm!E8</f>
+        <f>Cmi!E8-Cm!E8</f>
         <v>2</v>
       </c>
       <c r="F8">
-        <f>Cmi!F8-[1]Cm!F8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F8-Cm!F8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <f>Cmi!B9-[1]Cm!B9</f>
+        <f>Cmi!B9-Cm!B9</f>
         <v>0</v>
       </c>
       <c r="C9">
-        <f>Cmi!C9-[1]Cm!C9</f>
+        <f>Cmi!C9-Cm!C9</f>
         <v>0</v>
       </c>
       <c r="D9">
-        <f>Cmi!D9-[1]Cm!D9</f>
+        <f>Cmi!D9-Cm!D9</f>
         <v>0</v>
       </c>
       <c r="E9">
-        <f>Cmi!E9-[1]Cm!E9</f>
+        <f>Cmi!E9-Cm!E9</f>
         <v>0</v>
       </c>
       <c r="F9">
-        <f>Cmi!F9-[1]Cm!F9</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F9-Cm!F9</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <f>Cmi!B10-[1]Cm!B10</f>
+        <f>Cmi!B10-Cm!B10</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>Cmi!C10-[1]Cm!C10</f>
+        <f>Cmi!C10-Cm!C10</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f>Cmi!D10-[1]Cm!D10</f>
+        <f>Cmi!D10-Cm!D10</f>
         <v>-1</v>
       </c>
       <c r="E10">
-        <f>Cmi!E10-[1]Cm!E10</f>
+        <f>Cmi!E10-Cm!E10</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>Cmi!F10-[1]Cm!F10</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <f>Cmi!F10-Cm!F10</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
